--- a/Arbeitsjournal.xlsx
+++ b/Arbeitsjournal.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khalil Hamahmi\OneDrive - sluz\Dokumente\GitHub\Finanzappli\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brtoz\Codes\M306\Finanzappli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11B51B6-9925-4022-8C77-F3F098E21097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E87D7EA7-13D3-4F4F-9026-971F3349589B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{B78796A7-E541-485F-BCD7-E2AA158D2E78}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{B78796A7-E541-485F-BCD7-E2AA158D2E78}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="20">
   <si>
     <t>Wer?</t>
   </si>
@@ -87,6 +87,15 @@
   </si>
   <si>
     <t>Video</t>
+  </si>
+  <si>
+    <t>Berat, Zoé, Luka</t>
+  </si>
+  <si>
+    <t>Fertig</t>
+  </si>
+  <si>
+    <t>Projektauftrag Abgabe + Video</t>
   </si>
 </sst>
 </file>
@@ -138,7 +147,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -186,7 +195,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -502,14 +511,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0108AB90-790C-4EBE-825F-C791FBD723AC}">
-  <dimension ref="B3:G13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B3:G14"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="7" width="30.6328125" customWidth="1"/>
+    <col min="3" max="7" width="30.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -529,7 +538,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="2">
         <v>46080</v>
       </c>
@@ -543,7 +552,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
         <v>46080</v>
       </c>
@@ -560,7 +569,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="2">
         <v>46080</v>
       </c>
@@ -574,7 +583,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="2">
         <v>46080</v>
       </c>
@@ -591,7 +600,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="3">
         <v>46080</v>
       </c>
@@ -605,7 +614,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="3">
         <v>46108</v>
       </c>
@@ -619,7 +628,7 @@
         <v>46086</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="3">
         <v>46087</v>
       </c>
@@ -633,7 +642,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="3">
         <v>46087</v>
       </c>
@@ -647,7 +656,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="3">
         <v>46087</v>
       </c>
@@ -661,7 +670,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="3">
         <v>46087</v>
       </c>
@@ -673,6 +682,26 @@
       </c>
       <c r="E13" s="3">
         <v>46094</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="3">
+        <v>46087</v>
+      </c>
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="3">
+        <v>46087</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Arbeitsjournal.xlsx
+++ b/Arbeitsjournal.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brtoz\Codes\M306\Finanzappli\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Khalil Hamahmi\OneDrive - sluz\Dokumente\GitHub\Finanzappli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E87D7EA7-13D3-4F4F-9026-971F3349589B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A72396C3-AFA3-42A8-A911-9164524EE083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="17385" xr2:uid="{B78796A7-E541-485F-BCD7-E2AA158D2E78}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{B78796A7-E541-485F-BCD7-E2AA158D2E78}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="23">
   <si>
     <t>Wer?</t>
   </si>
@@ -92,10 +92,19 @@
     <t>Berat, Zoé, Luka</t>
   </si>
   <si>
-    <t>Fertig</t>
-  </si>
-  <si>
     <t>Projektauftrag Abgabe + Video</t>
+  </si>
+  <si>
+    <t>Berat, Zoé, Luka,Khalil</t>
+  </si>
+  <si>
+    <t>Stakeholderanalyse</t>
+  </si>
+  <si>
+    <t>Risikoanalyse</t>
+  </si>
+  <si>
+    <t>Nutzwerkanalyse</t>
   </si>
 </sst>
 </file>
@@ -147,7 +156,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -195,7 +204,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -511,14 +520,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0108AB90-790C-4EBE-825F-C791FBD723AC}">
-  <dimension ref="B3:G14"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B3:G17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="7" width="30.5703125" customWidth="1"/>
+    <col min="3" max="7" width="30.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
@@ -538,7 +547,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B4" s="2">
         <v>46080</v>
       </c>
@@ -552,7 +561,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B5" s="2">
         <v>46080</v>
       </c>
@@ -569,7 +578,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B6" s="2">
         <v>46080</v>
       </c>
@@ -583,7 +592,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B7" s="2">
         <v>46080</v>
       </c>
@@ -600,7 +609,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B8" s="3">
         <v>46080</v>
       </c>
@@ -613,8 +622,11 @@
       <c r="E8" s="3">
         <v>46086</v>
       </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B9" s="3">
         <v>46108</v>
       </c>
@@ -627,8 +639,11 @@
       <c r="E9" s="3">
         <v>46086</v>
       </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B10" s="3">
         <v>46087</v>
       </c>
@@ -642,7 +657,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B11" s="3">
         <v>46087</v>
       </c>
@@ -656,7 +671,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B12" s="3">
         <v>46087</v>
       </c>
@@ -670,7 +685,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B13" s="3">
         <v>46087</v>
       </c>
@@ -684,7 +699,7 @@
         <v>46094</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B14" s="3">
         <v>46087</v>
       </c>
@@ -698,10 +713,52 @@
         <v>46087</v>
       </c>
       <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" t="s">
         <v>18</v>
       </c>
-      <c r="G14" t="s">
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B15" s="3">
+        <v>46094</v>
+      </c>
+      <c r="C15" t="s">
         <v>19</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="3">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B16" s="3">
+        <v>46094</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="3">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B17" s="3">
+        <v>46101</v>
+      </c>
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="3">
+        <v>46101</v>
       </c>
     </row>
   </sheetData>
